--- a/artfynd/A 16226-2026 artfynd.xlsx
+++ b/artfynd/A 16226-2026 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132797103</v>
+        <v>132800759</v>
       </c>
       <c r="B3" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,34 +805,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Råberget, Lill-Råberget, Ång</t>
+          <t>Silkesmyran, Silkesmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686810</v>
+        <v>686851</v>
       </c>
       <c r="R3" t="n">
-        <v>7042184</v>
+        <v>7042117</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132800759</v>
+        <v>132797103</v>
       </c>
       <c r="B4" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,34 +912,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Silkesmyran, Silkesmyran, Ång</t>
+          <t>Lill-Råberget, Lill-Råberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686851</v>
+        <v>686810</v>
       </c>
       <c r="R4" t="n">
-        <v>7042117</v>
+        <v>7042184</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1128,53 +1128,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132806124</v>
+        <v>132807730</v>
       </c>
       <c r="B6" t="n">
-        <v>57145</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Råberget, Landsjösjön, Ång</t>
+          <t>lill-råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686837</v>
+        <v>686783</v>
       </c>
       <c r="R6" t="n">
-        <v>7042071</v>
+        <v>7042107</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera mindre bålar på högstubbe av björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,6 +1225,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1243,10 +1244,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132797675</v>
+        <v>132806124</v>
       </c>
       <c r="B7" t="n">
-        <v>97995</v>
+        <v>57145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,46 +1255,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Silkesmyran, Silkesmyran, Ång</t>
+          <t>Lill-Råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686692</v>
+        <v>686837</v>
       </c>
       <c r="R7" t="n">
-        <v>7042087</v>
+        <v>7042071</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,51 +1359,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132807730</v>
+        <v>132797675</v>
       </c>
       <c r="B8" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>lill-råberget, Landsjösjön, Ång</t>
+          <t>Silkesmyran, Silkesmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686783</v>
+        <v>686692</v>
       </c>
       <c r="R8" t="n">
-        <v>7042107</v>
+        <v>7042087</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera mindre bålar på högstubbe av björk</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1457,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16226-2026 artfynd.xlsx
+++ b/artfynd/A 16226-2026 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132800759</v>
+        <v>132797103</v>
       </c>
       <c r="B3" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -805,34 +805,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Silkesmyran, Silkesmyran, Ång</t>
+          <t>Lill-Råberget, Lill-Råberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686851</v>
+        <v>686810</v>
       </c>
       <c r="R3" t="n">
-        <v>7042117</v>
+        <v>7042184</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -901,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132797103</v>
+        <v>132800759</v>
       </c>
       <c r="B4" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,34 +912,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Råberget, Lill-Råberget, Ång</t>
+          <t>Silkesmyran, Silkesmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686810</v>
+        <v>686851</v>
       </c>
       <c r="R4" t="n">
-        <v>7042184</v>
+        <v>7042117</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -971,7 +971,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +981,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 16226-2026 artfynd.xlsx
+++ b/artfynd/A 16226-2026 artfynd.xlsx
@@ -1128,51 +1128,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132807730</v>
+        <v>132797675</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>lill-råberget, Landsjösjön, Ång</t>
+          <t>Silkesmyran, Silkesmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686783</v>
+        <v>686692</v>
       </c>
       <c r="R6" t="n">
-        <v>7042107</v>
+        <v>7042087</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera mindre bålar på högstubbe av björk</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1226,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,53 +1244,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132806124</v>
+        <v>132807730</v>
       </c>
       <c r="B7" t="n">
-        <v>57145</v>
+        <v>80438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Råberget, Landsjösjön, Ång</t>
+          <t>lill-råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686837</v>
+        <v>686783</v>
       </c>
       <c r="R7" t="n">
-        <v>7042071</v>
+        <v>7042107</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1322,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,7 +1327,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera mindre bålar på högstubbe av björk</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,6 +1341,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1359,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132797675</v>
+        <v>132806124</v>
       </c>
       <c r="B8" t="n">
-        <v>97995</v>
+        <v>57145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,46 +1371,45 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Silkesmyran, Silkesmyran, Ång</t>
+          <t>Lill-Råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686692</v>
+        <v>686837</v>
       </c>
       <c r="R8" t="n">
-        <v>7042087</v>
+        <v>7042071</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 16226-2026 artfynd.xlsx
+++ b/artfynd/A 16226-2026 artfynd.xlsx
@@ -1128,57 +1128,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132797675</v>
+        <v>132807730</v>
       </c>
       <c r="B6" t="n">
-        <v>97995</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Silkesmyran, Silkesmyran, Ång</t>
+          <t>lill-råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686692</v>
+        <v>686783</v>
       </c>
       <c r="R6" t="n">
-        <v>7042087</v>
+        <v>7042107</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera mindre bålar på högstubbe av björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,6 +1225,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1244,48 +1244,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132807730</v>
+        <v>132806124</v>
       </c>
       <c r="B7" t="n">
-        <v>80438</v>
+        <v>57145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>lill-råberget, Landsjösjön, Ång</t>
+          <t>Lill-Råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>686783</v>
+        <v>686837</v>
       </c>
       <c r="R7" t="n">
-        <v>7042107</v>
+        <v>7042071</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1327,12 +1332,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera mindre bålar på högstubbe av björk</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1341,7 +1341,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1359,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132806124</v>
+        <v>132797675</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>97995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1371,45 +1370,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Råberget, Landsjösjön, Ång</t>
+          <t>Silkesmyran, Silkesmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686837</v>
+        <v>686692</v>
       </c>
       <c r="R8" t="n">
-        <v>7042071</v>
+        <v>7042087</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 16226-2026 artfynd.xlsx
+++ b/artfynd/A 16226-2026 artfynd.xlsx
@@ -1128,51 +1128,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132807730</v>
+        <v>132797675</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>lill-råberget, Landsjösjön, Ång</t>
+          <t>Silkesmyran, Silkesmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686783</v>
+        <v>686692</v>
       </c>
       <c r="R6" t="n">
-        <v>7042107</v>
+        <v>7042087</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,7 +1207,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,12 +1217,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera mindre bålar på högstubbe av björk</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1225,7 +1226,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1359,57 +1359,51 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132797675</v>
+        <v>132807730</v>
       </c>
       <c r="B8" t="n">
-        <v>97995</v>
+        <v>80438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Silkesmyran, Silkesmyran, Ång</t>
+          <t>lill-råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686692</v>
+        <v>686783</v>
       </c>
       <c r="R8" t="n">
-        <v>7042087</v>
+        <v>7042107</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1438,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1442,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera mindre bålar på högstubbe av björk</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,6 +1456,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16226-2026 artfynd.xlsx
+++ b/artfynd/A 16226-2026 artfynd.xlsx
@@ -1128,57 +1128,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132797675</v>
+        <v>132807730</v>
       </c>
       <c r="B6" t="n">
-        <v>97995</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Silkesmyran, Silkesmyran, Ång</t>
+          <t>lill-råberget, Landsjösjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>686692</v>
+        <v>686783</v>
       </c>
       <c r="R6" t="n">
-        <v>7042087</v>
+        <v>7042107</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1217,7 +1211,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera mindre bålar på högstubbe av björk</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,6 +1225,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1359,51 +1359,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132807730</v>
+        <v>132797675</v>
       </c>
       <c r="B8" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>lill-råberget, Landsjösjön, Ång</t>
+          <t>Silkesmyran, Silkesmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>686783</v>
+        <v>686692</v>
       </c>
       <c r="R8" t="n">
-        <v>7042107</v>
+        <v>7042087</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1432,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,12 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Flera mindre bålar på högstubbe av björk</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1456,7 +1457,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 16226-2026 artfynd.xlsx
+++ b/artfynd/A 16226-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132795635</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -890,6 +900,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132800759</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132795652</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132798213</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132799255</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1346,6 +1376,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132806844</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132798725</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1569,6 +1609,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132807730</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1689,6 +1734,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132805976</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1804,6 +1854,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132806124</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1919,6 +1974,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132806384</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,6 +2094,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132806515</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2154,6 +2219,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132795509</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2270,8 +2340,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132797675</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>